--- a/Packages/cn.etetet.skill/Luban/Config/Datas/ActionEventConfig.xlsx
+++ b/Packages/cn.etetet.skill/Luban/Config/Datas/ActionEventConfig.xlsx
@@ -9,9 +9,103 @@
   <sheets>
     <sheet name="ActionEventConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>ActionEventType</t>
+  </si>
+  <si>
+    <t>IsClientOnly</t>
+  </si>
+  <si>
+    <t>Params</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>EActionEventType</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>ActionEventParams</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>事件ID</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>事件类型</t>
+  </si>
+  <si>
+    <t>仅客户端</t>
+  </si>
+  <si>
+    <t>参数(多态)</t>
+  </si>
+  <si>
+    <t>SpitBall</t>
+  </si>
+  <si>
+    <t>吐球</t>
+  </si>
+  <si>
+    <t>BallSpit</t>
+  </si>
+  <si>
+    <t>ET.ActionEventParams_BallSpit</t>
+  </si>
+  <si>
+    <t>Split</t>
+  </si>
+  <si>
+    <t>分裂</t>
+  </si>
+  <si>
+    <t>BallSplit</t>
+  </si>
+  <si>
+    <t>ET.ActionEventParams_BallSplit</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19,16 +113,16 @@
   <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,10 +141,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -408,175 +502,483 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Desc</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ActionEventType</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>IsClientOnly</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Params</t>
-        </is>
-      </c>
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1"/>
+      <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
+      <c r="O1"/>
+      <c r="P1"/>
+      <c r="Q1"/>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1"/>
+      <c r="W1"/>
+      <c r="X1"/>
+      <c r="Y1"/>
+      <c r="Z1"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>list,int</t>
-        </is>
-      </c>
+      <c r="A2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
-      </c>
+      <c r="A3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>事件ID</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>名字</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>事件类型(8吐球 9分裂)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>仅客户端</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>参数</t>
-        </is>
-      </c>
+      <c r="A4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4"/>
     </row>
     <row r="5">
-      <c r="B5" t="n">
+      <c r="A5" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="0">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SpitBall</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>吐球</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" t="b">
+      <c r="C5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="G5" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="0">
+        <v>50</v>
+      </c>
+      <c r="I5" s="0">
+        <v>30</v>
+      </c>
+      <c r="J5" s="0">
+        <v>30</v>
+      </c>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5"/>
     </row>
     <row r="6">
-      <c r="B6" t="n">
+      <c r="A6" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="0">
         <v>2</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Split</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>分裂</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" t="b">
+      <c r="C6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="G6" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="0">
+        <v>200</v>
+      </c>
+      <c r="I6" s="0">
+        <v>25</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+      <c r="Z8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
+      <c r="Z9"/>
+    </row>
+    <row r="10">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
+      <c r="Z10"/>
+    </row>
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11"/>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
+      <c r="Z11"/>
+    </row>
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
+      <c r="Z12"/>
     </row>
   </sheetData>
+  <mergeCells>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G4:J4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>